--- a/lite/dist/20261025_Lumentum模型_v0.2.xlsx
+++ b/lite/dist/20261025_Lumentum模型_v0.2.xlsx
@@ -4436,7 +4436,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4654,7 +4654,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4775,7 +4775,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4896,7 +4896,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5017,7 +5017,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5138,7 +5138,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
